--- a/AI Audit Log_PhanNhatNam.xlsx
+++ b/AI Audit Log_PhanNhatNam.xlsx
@@ -5,18 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SWD392\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\GitHub\ai-audit-log-nambautroi00\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F66FF22-B5AA-4648-AC1D-40396E86A28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC8E584-6D11-4C15-8AAE-838E4E3332F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3945" yWindow="2670" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Week 1" sheetId="2" r:id="rId2"/>
     <sheet name="Week 2" sheetId="3" r:id="rId3"/>
     <sheet name="Week 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="5" r:id="rId5"/>
+    <sheet name="Week 5" sheetId="6" r:id="rId6"/>
+    <sheet name="Week 6" sheetId="7" r:id="rId7"/>
+    <sheet name="Week 7" sheetId="8" r:id="rId8"/>
+    <sheet name="Week 8" sheetId="9" r:id="rId9"/>
+    <sheet name="Week 9" sheetId="10" r:id="rId10"/>
+    <sheet name="Week 10" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="140">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -300,6 +307,180 @@
   <si>
     <t>Phản hồi AI: AI đề xuất mở rộng telemedicine, AI recommendation, chatbot hỗ trợ và dashboard analytics cho bệnh viện.
 Quyết định: Tôi xác định các chức năng này phù hợp cho hướng phát triển dài hạn, tuy nhiên ở phạm vi hiện tại tôi sẽ tập trung hoàn thiện booking workflow và quản lý lịch hẹn trước.</t>
+  </si>
+  <si>
+    <t>Nêu rõ giống nhau hoặc khác nhau của AI &amp; phần bài PE của tôi</t>
+  </si>
+  <si>
+    <t>So sánh bài tự làm với bài AI hỗ trợ trong PE SWD392</t>
+  </si>
+  <si>
+    <t>“So sánh Class Diagram do tôi tự thiết kế với Class Diagram do AI đề xuất cho hệ thống AutoGo car rental.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng các class chính như User, Customer, Staff, Booking, Car và Payment. Cả hai đều áp dụng Repository Pattern và sử dụng inheritance giữa User với Customer và Staff. Khác nhau: AI thiết kế diagram theo hướng tổng quát và chưa tối ưu một số multiplicity relationship. Trong bài PE của tôi, tôi chỉnh sửa lại association giữa Booking và Payment để sát hơn với business workflow thực tế và đúng tiêu chí UML design-level của môn SWD392.</t>
+  </si>
+  <si>
+    <t>“So sánh cách xây dựng Sequence Diagram giữa bài tự làm và bài AI hỗ trợ.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng Layered Architecture với các thành phần UI, Controller, Service, Repository và Entity. Hai diagram đều có alt fragment cho trường hợp car availability và payment result. Khác nhau: AI sắp xếp một số bước xử lý chưa hoàn toàn đúng với quy trình business thực tế. Trong bài PE của tôi, tôi chỉnh lại thứ tự xử lý booking và payment để flow logic rõ ràng hơn.</t>
+  </si>
+  <si>
+    <t>“So sánh Activity Diagram Return Car do AI tạo với bài tôi tự hoàn thiện.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả hai diagram đều có swimlane Staff và System, đều sử dụng decision node để xác định additional fee. Khác nhau: AI chỉ mô tả workflow ở mức cơ bản, còn bài PE của tôi bổ sung thêm bước nhận remaining payment và update car status để workflow đầy đủ hơn.</t>
+  </si>
+  <si>
+    <t>“So sánh việc áp dụng Repository Pattern giữa bài AI và bài tôi tự chỉnh sửa.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng IRepository và các repository implementation như BookingRepository, PaymentRepository và CarRepository. Khác nhau: AI chủ yếu tập trung vào cấu trúc repository, trong khi bài PE của tôi thể hiện rõ dependency relationship giữa service layer và repository layer để diagram trực quan hơn.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi xác định các relationship UML trong Class Diagram.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng inheritance, association, aggregation và composition đúng yêu cầu đề bài. Khác nhau: AI sử dụng một số hướng association chưa trực quan, còn bài PE của tôi điều chỉnh lại multiplicity và hướng relationship để dễ đọc và dễ trình bày hơn khi bảo vệ bài.</t>
+  </si>
+  <si>
+    <t>“So sánh phần business workflow giữa bài AI và bài tự làm.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả hai đều mô tả quy trình booking, payment và return car dựa trên business context của hệ thống AutoGo. Khác nhau: AI mô tả workflow theo hướng khái quát, trong khi bài PE của tôi bổ sung thêm các trạng thái booking như CONFIRMED, CANCELLED và COMPLETED để thể hiện đầy đủ lifecycle của booking.</t>
+  </si>
+  <si>
+    <t>“So sánh cách lựa chọn kiến trúc hệ thống giữa AI và quyết định của tôi.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: AI và bài PE của tôi đều xác định Layered Architecture là phù hợp với yêu cầu đề thi. Khác nhau: AI cũng đề xuất Microservices Architecture như một lựa chọn thay thế, còn bài PE của tôi chỉ tập trung vào Layered Architecture để giữ tính nhất quán giữa các UML diagrams và tránh làm hệ thống quá phức tạp trong phạm vi PE.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi thiết kế service layer trong hệ thống.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng PaymentService để xử lý payment business logic. Khác nhau: AI chưa phân tách rõ responsibility giữa Controller và Service trong một số interaction, còn bài PE của tôi tách riêng Controller để điều phối luồng xử lý và Service để xử lý business logic nhằm đúng với layered design principle.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi xử lý điều kiện payment success/failure trong Sequence Diagram.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả hai đều sử dụng alt fragment để xử lý hai trường hợp payment success và payment failure. Khác nhau: AI chưa mô tả rõ rollback workflow khi payment thất bại, trong khi bài PE của tôi bổ sung thêm bước cancel booking và update booking status = CANCELLED để workflow hoàn chỉnh hơn.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi thiết kế swimlane trong Activity Diagram.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều chia swimlane thành Staff và System theo đúng yêu cầu đề bài. Khác nhau: AI trình bày workflow theo hướng tổng quát, còn bài PE của tôi phân chia rõ trách nhiệm giữa actor và system để dễ theo dõi quá trình xử lý hơn.</t>
+  </si>
+  <si>
+    <t>“So sánh naming convention giữa bài AI và bài tự làm.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng naming convention theo hướng object-oriented design. Khác nhau: AI sử dụng một số method name còn khá generic như create() hoặc updateStatus(), trong khi bài PE của tôi điều chỉnh method name cụ thể hơn để sát với business context của car rental system.</t>
+  </si>
+  <si>
+    <t>“So sánh mức độ chi tiết của bài AI và bài tôi hoàn thiện.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều đáp ứng đầy đủ các yêu cầu UML chính của đề thi SWD392. Khác nhau: AI tập trung vào việc tạo nhanh skeleton UML, còn bài PE của tôi bổ sung thêm nhiều business detail để diagram sát với thực tế và rubric chấm điểm hơn.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi xử lý business logic trong Return Car workflow.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả hai đều mô tả bước inspect car, calculate additional fee và update booking status. Khác nhau: AI chưa nhấn mạnh bước update car status sau khi hoàn thành return process, trong khi bài PE của tôi bổ sung bước update car status = Available để workflow kết thúc hợp lý hơn.</t>
+  </si>
+  <si>
+    <t>“So sánh việc sử dụng UML notation giữa AI và bài tôi chỉnh sửa.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng đúng UML notation như inheritance, dependency, composition và alt fragment. Khác nhau: AI đôi khi sử dụng notation theo hướng mặc định, còn bài PE của tôi điều chỉnh lại notation để trực quan hơn và phù hợp với design-level UML diagram trong SWD392.</t>
+  </si>
+  <si>
+    <t>“So sánh khả năng hỗ trợ brainstorming của AI với quá trình tự thiết kế UML.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều hướng tới mục tiêu hoàn thành đúng business requirement của đề thi AutoGo car rental system. Khác nhau: AI hỗ trợ rất nhanh trong việc đề xuất structure và workflow ban đầu, nhưng một số phần còn mang tính khái quát. Trong bài PE của tôi, tôi tự điều chỉnh lại relationship, workflow và naming convention để phù hợp hơn với yêu cầu thực tế và tiêu chí chấm điểm của môn SWD392.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi thiết kế trạng thái của Booking trong hệ thống.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng các trạng thái cơ bản như CONFIRMED và CANCELLED để quản lý booking workflow. Khác nhau: AI chỉ đề xuất các trạng thái ở mức tổng quát, còn bài PE của tôi bổ sung thêm COMPLETED và PENDING PAYMENT để thể hiện đầy đủ lifecycle của booking trong cả Sequence Diagram và Activity Diagram.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi mô hình hóa Payment trong hệ thống AutoGo.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều xem Payment là thành phần liên quan trực tiếp đến Booking và đều sử dụng PaymentService để xử lý payment logic. Khác nhau: AI tập trung nhiều vào transaction flow, còn bài PE của tôi nhấn mạnh thêm relationship giữa Payment và Booking bằng composition để đúng UML design principle hơn.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi xử lý trường hợp car unavailable.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng alt fragment để xử lý trường hợp xe không khả dụng. Khác nhau: AI chỉ trả về unavailable message đơn giản, trong khi bài PE của tôi bổ sung thêm bước dừng workflow ngay sau khi kiểm tra availability để tránh tạo booking không hợp lệ.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi biểu diễn dependency relationship trong UML.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng dependency relationship giữa service layer và repository layer. Khác nhau: AI biểu diễn dependency theo hướng tối giản, còn bài PE của tôi làm rõ dependency bằng stereotype và hướng mũi tên để diagram trực quan hơn khi trình bày.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi thiết kế entity attributes trong Class Diagram.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng các thuộc tính cơ bản như bookingId, paymentId, carId và status. Khác nhau: AI đề xuất nhiều attribute mang tính generic, còn bài PE của tôi lựa chọn attribute phù hợp trực tiếp với business requirement của AutoGo để tránh diagram bị quá tải.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi xử lý role của Staff trong hệ thống.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều xác định Staff có trách nhiệm inspect car và confirm booking. Khác nhau: AI mô tả Staff theo hướng đơn giản, còn bài PE của tôi bổ sung thêm responsibility update vehicle status để phản ánh đúng business workflow return car.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi tổ chức các layer trong hệ thống.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều chia hệ thống thành Presentation Layer, Service Layer và Repository Layer. Khác nhau: AI mô tả layer ở mức lý thuyết tổng quát, còn bài PE của tôi liên kết trực tiếp từng layer với các thành phần UML cụ thể như BookingUI, BookingController và Repository classes để dễ hiểu hơn.</t>
+  </si>
+  <si>
+    <t>“So sánh mức độ thực tế của business workflow giữa AI và bài tự làm.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều dựa trên nghiệp vụ thuê xe thực tế gồm booking, payment và return car. Khác nhau: AI tạo workflow theo hướng học thuật tổng quát, còn bài PE của tôi điều chỉnh workflow để sát với quy trình business thực tế hơn như pending payment, remaining fee và vehicle status update.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi trình bày UML diagram trong bài PE.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều sử dụng đúng UML notation và đảm bảo đầy đủ các thành phần bắt buộc của đề bài. Khác nhau: AI ưu tiên tốc độ sinh diagram nên bố cục đôi khi chưa cân đối, còn bài PE của tôi sắp xếp lại layout diagram để trực quan hơn và dễ đọc hơn khi giảng viên chấm bài.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi xử lý exception flow trong hệ thống.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều có xử lý các trường hợp exception như payment failure hoặc unavailable car. Khác nhau: AI xử lý exception ở mức cơ bản, còn bài PE của tôi bổ sung thêm update booking status và terminate workflow để đảm bảo tính consistency của hệ thống.</t>
+  </si>
+  <si>
+    <t>“So sánh khả năng tối ưu diagram giữa AI và bài tôi tự chỉnh sửa.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều đảm bảo đầy đủ yêu cầu UML của đề SWD392. Khác nhau: AI có xu hướng thêm nhiều thành phần để diagram đầy đủ hơn, còn bài PE của tôi tối giản các thành phần không cần thiết để diagram dễ nhìn và phù hợp với thời gian làm PE.</t>
+  </si>
+  <si>
+    <t>“So sánh cách AI và tôi xử lý business validation trong booking process.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều thực hiện bước kiểm tra car availability trước khi tạo booking. Khác nhau: AI chỉ mô tả validation ở mức repository call, còn bài PE của tôi nhấn mạnh validation là điều kiện bắt buộc trước khi chuyển sang payment workflow.</t>
+  </si>
+  <si>
+    <t>“So sánh vai trò hỗ trợ của AI trong quá trình làm PE SWD392.”</t>
+  </si>
+  <si>
+    <t>Giống nhau: Cả AI và bài PE của tôi đều hướng tới mục tiêu xây dựng UML diagrams đúng business requirement của đề AutoGo. Khác nhau: AI hỗ trợ nhanh trong việc tạo skeleton UML và đề xuất workflow ban đầu, còn bài PE của tôi tập trung vào việc điều chỉnh lại diagram để đúng business logic, rubric chấm điểm và phong cách trình bày UML mà giảng viên yêu cầu trong môn SWD392.</t>
   </si>
 </sst>
 </file>
@@ -415,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -441,16 +622,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -470,10 +642,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -893,9 +1073,27 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83D33498-89EE-4A63-9385-22EC826AFB59}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{621937BF-6CCF-4B32-A32C-F313A456CB1D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -919,122 +1117,116 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="165" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="16" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="135" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="136.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="15">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="13" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1124,69 +1316,69 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="9" t="s">
         <v>53</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+    <row r="7" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+    <row r="8" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="6" t="s">
         <v>59</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+    <row r="9" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+    <row r="10" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -1194,52 +1386,52 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+    <row r="12" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+    <row r="13" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
+    <row r="14" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="3" t="s">
         <v>76</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -1250,13 +1442,13 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="6" t="s">
         <v>80</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -1270,11 +1462,466 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="36.42578125" customWidth="1"/>
+    <col min="4" max="4" width="62.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
+        <v>6</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
+        <v>7</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
+        <v>8</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
+        <v>9</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>11</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
+        <v>12</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>13</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
+        <v>14</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
+        <v>15</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
+        <v>16</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
+        <v>17</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>19</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
+        <v>20</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
+        <v>21</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
+        <v>22</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
+        <v>23</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
+        <v>24</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
+        <v>25</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
+        <v>26</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
+        <v>27</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
+        <v>28</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EA285CC-65AF-4573-AD9B-A5F5BAEA2993}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="4" width="9.140625" customWidth="1"/>
-  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0D9DBE-B3E5-41BB-92F5-446F369CB16D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A719C98-F48B-4C65-8EDA-3EB5CA29F09A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A75C0C-8A23-4CF2-8278-5C7D19769789}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4F0A044-0AE3-4527-9B4F-CF5CC2B3511D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
